--- a/Сценарий к презентации для конференции HR 2026 КУ с цифрами.xlsx
+++ b/Сценарий к презентации для конференции HR 2026 КУ с цифрами.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artemnikiforov/Desktop/Code/конференция/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A861A6FB-D535-1D44-BCF9-A54A60A97DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BE9234-6B38-154D-921C-A04C4D2CD7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{893D6B5D-D39B-4392-AB2A-B07679F30FA6}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{893D6B5D-D39B-4392-AB2A-B07679F30FA6}"/>
   </bookViews>
   <sheets>
     <sheet name="ФИНАЛ" sheetId="4" r:id="rId1"/>
@@ -1498,16 +1498,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>2305050</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1060450</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>109538</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>7938</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1536,8 +1536,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2305050" y="22656800"/>
-          <a:ext cx="5003800" cy="2814638"/>
+          <a:off x="9747250" y="22244050"/>
+          <a:ext cx="5575300" cy="2909888"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
